--- a/complete/FINAL_NYAHURURU_LOANS_COMPLETE.xlsx
+++ b/complete/FINAL_NYAHURURU_LOANS_COMPLETE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\KashLeo data\complete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7B2B4C-D282-4C31-9630-8E7D494506E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D93B6E-E5C3-48D8-8059-3E8E32CFB65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4971,6 +4971,9 @@
       <c r="C61">
         <v>721111140</v>
       </c>
+      <c r="D61">
+        <v>25332821</v>
+      </c>
       <c r="E61" t="s">
         <v>165</v>
       </c>
@@ -4978,7 +4981,7 @@
         <v>712561516</v>
       </c>
       <c r="G61">
-        <v>2134179</v>
+        <v>33531770</v>
       </c>
       <c r="H61">
         <v>7000</v>
